--- a/data/raw/scenarios/soy-scenarios-10-24.xlsx
+++ b/data/raw/scenarios/soy-scenarios-10-24.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2026349847773/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\efelli\Documents\GitHub\soybean-ar-climate-change\data\raw\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{6C62109E-3BC4-4521-B4F9-2FC772C2F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3FBDC62-1B2B-4404-B498-90A21F58855E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990AF1C6-3180-4BFD-83D3-CF2C04448DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,10 +88,10 @@
     <t>1/1/1980</t>
   </si>
   <si>
-    <t>15-Apr</t>
-  </si>
-  <si>
-    <t>15-May</t>
+    <t>06-May</t>
+  </si>
+  <si>
+    <t>08-Apr</t>
   </si>
 </sst>
 </file>
@@ -468,7 +468,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>12</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>13</v>
@@ -520,7 +520,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>14</v>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -598,7 +598,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>13</v>
@@ -624,7 +624,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -650,7 +650,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>15</v>
@@ -676,7 +676,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>

--- a/data/raw/scenarios/soy-scenarios-10-24.xlsx
+++ b/data/raw/scenarios/soy-scenarios-10-24.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\efelli\Documents\GitHub\soybean-ar-climate-change\data\raw\scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\efelli\Documents\GitHub\data\raw\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990AF1C6-3180-4BFD-83D3-CF2C04448DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C26420-5076-4784-B38F-99636E68E52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8300" yWindow="6740" windowWidth="25580" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,10 +88,10 @@
     <t>1/1/1980</t>
   </si>
   <si>
-    <t>06-May</t>
-  </si>
-  <si>
-    <t>08-Apr</t>
+    <t>22-May</t>
+  </si>
+  <si>
+    <t>24-Apr</t>
   </si>
 </sst>
 </file>
